--- a/feature/refonte-documentation-validateurs/ig/ValueSet-sas-valueset-appointmentreason.xlsx
+++ b/feature/refonte-documentation-validateurs/ig/ValueSet-sas-valueset-appointmentreason.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T08:37:37+00:00</t>
+    <t>2026-07-07T11:45:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/refonte-documentation-validateurs/ig/ValueSet-sas-valueset-appointmentreason.xlsx
+++ b/feature/refonte-documentation-validateurs/ig/ValueSet-sas-valueset-appointmentreason.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T11:45:50+00:00</t>
+    <t>2026-07-07T12:24:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/refonte-documentation-validateurs/ig/ValueSet-sas-valueset-appointmentreason.xlsx
+++ b/feature/refonte-documentation-validateurs/ig/ValueSet-sas-valueset-appointmentreason.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T12:24:20+00:00</t>
+    <t>2026-07-08T16:00:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
